--- a/cypress/downloads/Visit_Report_store_2026-05-12.xlsx
+++ b/cypress/downloads/Visit_Report_store_2026-05-12.xlsx
@@ -460,34 +460,34 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>K2 Jaya</v>
+        <v>Maju Jaya (Sukolilo)</v>
       </c>
       <c r="B2" t="str">
-        <v>K2 Jaya</v>
+        <v>Maju Jaya (Sukolilo)</v>
       </c>
       <c r="C2" t="str">
         <v>Others</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" t="str">
-        <v>-20.0%</v>
+        <v>150.0%</v>
       </c>
       <c r="G2">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2">
         <v>0</v>

--- a/cypress/downloads/Visit_Report_store_2026-05-12.xlsx
+++ b/cypress/downloads/Visit_Report_store_2026-05-12.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:S103"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -460,66 +460,6025 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>K2 Jaya</v>
+      </c>
+      <c r="B2" t="str">
+        <v>K2 Jaya</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D2">
+        <v>10</v>
+      </c>
+      <c r="E2">
+        <v>10</v>
+      </c>
+      <c r="F2" t="str">
+        <v>0.0%</v>
+      </c>
+      <c r="G2">
+        <v>20</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>maju jaya</v>
+      </c>
+      <c r="B3" t="str">
+        <v>maju jaya</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>15</v>
+      </c>
+      <c r="F3" t="str">
+        <v>200.0%</v>
+      </c>
+      <c r="G3">
+        <v>20</v>
+      </c>
+      <c r="H3">
+        <v>6</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>makmur jaya</v>
+      </c>
+      <c r="B4" t="str">
+        <v>makmur jaya</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>13</v>
+      </c>
+      <c r="F4" t="str">
+        <v>160.0%</v>
+      </c>
+      <c r="G4">
+        <v>18</v>
+      </c>
+      <c r="H4">
+        <v>6</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>surya cipta</v>
+      </c>
+      <c r="B5" t="str">
+        <v>surya cipta</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>14</v>
+      </c>
+      <c r="F5" t="str">
+        <v>250.0%</v>
+      </c>
+      <c r="G5">
+        <v>18</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>ACC</v>
+      </c>
+      <c r="B6" t="str">
+        <v>ACC</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6" t="str">
+        <v>83.3%</v>
+      </c>
+      <c r="G6">
+        <v>17</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>sinar abadi</v>
+      </c>
+      <c r="B7" t="str">
+        <v>sinar abadi</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+      <c r="E7">
+        <v>11</v>
+      </c>
+      <c r="F7" t="str">
+        <v>83.3%</v>
+      </c>
+      <c r="G7">
+        <v>17</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7">
+        <v>3</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>sinar samudra</v>
+      </c>
+      <c r="B8" t="str">
+        <v>sinar samudra</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D8">
+        <v>6</v>
+      </c>
+      <c r="E8">
+        <v>11</v>
+      </c>
+      <c r="F8" t="str">
+        <v>83.3%</v>
+      </c>
+      <c r="G8">
+        <v>17</v>
+      </c>
+      <c r="H8">
+        <v>4</v>
+      </c>
+      <c r="I8">
+        <v>3</v>
+      </c>
+      <c r="J8">
+        <v>3</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>S</v>
+      </c>
+      <c r="B9" t="str">
+        <v>S</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="E9">
+        <v>12</v>
+      </c>
+      <c r="F9" t="str">
+        <v>200.0%</v>
+      </c>
+      <c r="G9">
+        <v>16</v>
+      </c>
+      <c r="H9">
+        <v>4</v>
+      </c>
+      <c r="I9">
+        <v>4</v>
+      </c>
+      <c r="J9">
+        <v>3</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>mubarok</v>
+      </c>
+      <c r="B10" t="str">
+        <v>mubarok</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D10">
+        <v>8</v>
+      </c>
+      <c r="E10">
+        <v>8</v>
+      </c>
+      <c r="F10" t="str">
+        <v>0.0%</v>
+      </c>
+      <c r="G10">
+        <v>16</v>
+      </c>
+      <c r="H10">
+        <v>3</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="J10">
+        <v>3</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>ahmad</v>
+      </c>
+      <c r="B11" t="str">
+        <v>ahmad</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D11">
+        <v>6</v>
+      </c>
+      <c r="E11">
+        <v>9</v>
+      </c>
+      <c r="F11" t="str">
+        <v>50.0%</v>
+      </c>
+      <c r="G11">
+        <v>15</v>
+      </c>
+      <c r="H11">
+        <v>3</v>
+      </c>
+      <c r="I11">
+        <v>2</v>
+      </c>
+      <c r="J11">
+        <v>3</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>jaya makmur</v>
+      </c>
+      <c r="B12" t="str">
+        <v>jaya makmur</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D12">
+        <v>7</v>
+      </c>
+      <c r="E12">
+        <v>7</v>
+      </c>
+      <c r="F12" t="str">
+        <v>0.0%</v>
+      </c>
+      <c r="G12">
+        <v>14</v>
+      </c>
+      <c r="H12">
+        <v>4</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Bima Suci</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Bima Suci</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+      <c r="E13">
+        <v>8</v>
+      </c>
+      <c r="F13" t="str">
+        <v>60.0%</v>
+      </c>
+      <c r="G13">
+        <v>13</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>2</v>
+      </c>
+      <c r="J13">
+        <v>3</v>
+      </c>
+      <c r="K13">
+        <v>2</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>KARYA INDAH II</v>
+      </c>
+      <c r="B14" t="str">
+        <v>KARYA INDAH II</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D14">
+        <v>3</v>
+      </c>
+      <c r="E14">
+        <v>10</v>
+      </c>
+      <c r="F14" t="str">
+        <v>233.3%</v>
+      </c>
+      <c r="G14">
+        <v>13</v>
+      </c>
+      <c r="H14">
+        <v>2</v>
+      </c>
+      <c r="I14">
+        <v>2</v>
+      </c>
+      <c r="J14">
+        <v>4</v>
+      </c>
+      <c r="K14">
+        <v>2</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>MURNI PAPAN</v>
+      </c>
+      <c r="B15" t="str">
+        <v>MURNI PAPAN</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="E15">
+        <v>9</v>
+      </c>
+      <c r="F15" t="str">
+        <v>125.0%</v>
+      </c>
+      <c r="G15">
+        <v>13</v>
+      </c>
+      <c r="H15">
+        <v>2</v>
+      </c>
+      <c r="I15">
+        <v>3</v>
+      </c>
+      <c r="J15">
+        <v>3</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Putra borneo</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Putra borneo</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16">
+        <v>11</v>
+      </c>
+      <c r="F16" t="str">
+        <v>450.0%</v>
+      </c>
+      <c r="G16">
+        <v>13</v>
+      </c>
+      <c r="H16">
+        <v>4</v>
+      </c>
+      <c r="I16">
+        <v>3</v>
+      </c>
+      <c r="J16">
+        <v>3</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Cakrawala</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Cakrawala</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D17">
+        <v>4</v>
+      </c>
+      <c r="E17">
+        <v>8</v>
+      </c>
+      <c r="F17" t="str">
+        <v>100.0%</v>
+      </c>
+      <c r="G17">
+        <v>12</v>
+      </c>
+      <c r="H17">
+        <v>2</v>
+      </c>
+      <c r="I17">
+        <v>2</v>
+      </c>
+      <c r="J17">
+        <v>3</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Makmur Jaya</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Makmur Jaya</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D18">
+        <v>2</v>
+      </c>
+      <c r="E18">
+        <v>10</v>
+      </c>
+      <c r="F18" t="str">
+        <v>400.0%</v>
+      </c>
+      <c r="G18">
+        <v>12</v>
+      </c>
+      <c r="H18">
+        <v>4</v>
+      </c>
+      <c r="I18">
+        <v>4</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Rini</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Rini</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D19">
+        <v>4</v>
+      </c>
+      <c r="E19">
+        <v>8</v>
+      </c>
+      <c r="F19" t="str">
+        <v>100.0%</v>
+      </c>
+      <c r="G19">
+        <v>12</v>
+      </c>
+      <c r="H19">
+        <v>3</v>
+      </c>
+      <c r="I19">
+        <v>3</v>
+      </c>
+      <c r="J19">
+        <v>2</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>SLR MAKMUR SURABAYA</v>
+      </c>
+      <c r="B20" t="str">
+        <v>SLR MAKMUR SURABAYA</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
+      <c r="E20">
+        <v>10</v>
+      </c>
+      <c r="F20" t="str">
+        <v>400.0%</v>
+      </c>
+      <c r="G20">
+        <v>12</v>
+      </c>
+      <c r="H20">
+        <v>2</v>
+      </c>
+      <c r="I20">
+        <v>4</v>
+      </c>
+      <c r="J20">
+        <v>3</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>aries jaya</v>
+      </c>
+      <c r="B21" t="str">
+        <v>aries jaya</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D21">
+        <v>3</v>
+      </c>
+      <c r="E21">
+        <v>9</v>
+      </c>
+      <c r="F21" t="str">
+        <v>200.0%</v>
+      </c>
+      <c r="G21">
+        <v>12</v>
+      </c>
+      <c r="H21">
+        <v>2</v>
+      </c>
+      <c r="I21">
+        <v>3</v>
+      </c>
+      <c r="J21">
+        <v>3</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>gangsar jaya</v>
+      </c>
+      <c r="B22" t="str">
+        <v>gangsar jaya</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D22">
+        <v>4</v>
+      </c>
+      <c r="E22">
+        <v>8</v>
+      </c>
+      <c r="F22" t="str">
+        <v>100.0%</v>
+      </c>
+      <c r="G22">
+        <v>12</v>
+      </c>
+      <c r="H22">
+        <v>3</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>3</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>muncul abadi 2</v>
+      </c>
+      <c r="B23" t="str">
+        <v>muncul abadi 2</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D23">
+        <v>4</v>
+      </c>
+      <c r="E23">
+        <v>8</v>
+      </c>
+      <c r="F23" t="str">
+        <v>100.0%</v>
+      </c>
+      <c r="G23">
+        <v>12</v>
+      </c>
+      <c r="H23">
+        <v>3</v>
+      </c>
+      <c r="I23">
+        <v>2</v>
+      </c>
+      <c r="J23">
+        <v>2</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>BERKAT JAYA LONTAR</v>
+      </c>
+      <c r="B24" t="str">
+        <v>BERKAT JAYA LONTAR</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D24">
+        <v>3</v>
+      </c>
+      <c r="E24">
+        <v>8</v>
+      </c>
+      <c r="F24" t="str">
+        <v>166.7%</v>
+      </c>
+      <c r="G24">
+        <v>11</v>
+      </c>
+      <c r="H24">
+        <v>3</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>3</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>BUMI JAYA BENOWO</v>
+      </c>
+      <c r="B25" t="str">
+        <v>BUMI JAYA BENOWO</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D25">
+        <v>4</v>
+      </c>
+      <c r="E25">
+        <v>7</v>
+      </c>
+      <c r="F25" t="str">
+        <v>75.0%</v>
+      </c>
+      <c r="G25">
+        <v>11</v>
+      </c>
+      <c r="H25">
+        <v>3</v>
+      </c>
+      <c r="I25">
+        <v>2</v>
+      </c>
+      <c r="J25">
+        <v>2</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Bumi jaya</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Bumi jaya</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D26">
+        <v>7</v>
+      </c>
+      <c r="E26">
+        <v>4</v>
+      </c>
+      <c r="F26" t="str">
+        <v>-42.9%</v>
+      </c>
+      <c r="G26">
+        <v>11</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="J26">
+        <v>2</v>
+      </c>
+      <c r="K26">
+        <v>1</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Lintang</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Lintang</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D27">
+        <v>4</v>
+      </c>
+      <c r="E27">
+        <v>7</v>
+      </c>
+      <c r="F27" t="str">
+        <v>75.0%</v>
+      </c>
+      <c r="G27">
+        <v>11</v>
+      </c>
+      <c r="H27">
+        <v>3</v>
+      </c>
+      <c r="I27">
+        <v>2</v>
+      </c>
+      <c r="J27">
+        <v>2</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>MAKMUR JAYA</v>
+      </c>
+      <c r="B28" t="str">
+        <v>MAKMUR JAYA</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D28">
+        <v>4</v>
+      </c>
+      <c r="E28">
+        <v>7</v>
+      </c>
+      <c r="F28" t="str">
+        <v>75.0%</v>
+      </c>
+      <c r="G28">
+        <v>11</v>
+      </c>
+      <c r="H28">
+        <v>4</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="J28">
+        <v>2</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>SUMBER BAHAGIA</v>
+      </c>
+      <c r="B29" t="str">
+        <v>SUMBER BAHAGIA</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D29">
+        <v>6</v>
+      </c>
+      <c r="E29">
+        <v>5</v>
+      </c>
+      <c r="F29" t="str">
+        <v>-16.7%</v>
+      </c>
+      <c r="G29">
+        <v>11</v>
+      </c>
+      <c r="H29">
+        <v>3</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>2</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Sentral Utama</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Sentral Utama</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D30">
+        <v>3</v>
+      </c>
+      <c r="E30">
+        <v>8</v>
+      </c>
+      <c r="F30" t="str">
+        <v>166.7%</v>
+      </c>
+      <c r="G30">
+        <v>11</v>
+      </c>
+      <c r="H30">
+        <v>2</v>
+      </c>
+      <c r="I30">
+        <v>3</v>
+      </c>
+      <c r="J30">
+        <v>3</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>BARI JAYA MANUKAN</v>
+      </c>
+      <c r="B31" t="str">
+        <v>BARI JAYA MANUKAN</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D31">
+        <v>3</v>
+      </c>
+      <c r="E31">
+        <v>7</v>
+      </c>
+      <c r="F31" t="str">
+        <v>133.3%</v>
+      </c>
+      <c r="G31">
+        <v>10</v>
+      </c>
+      <c r="H31">
+        <v>3</v>
+      </c>
+      <c r="I31">
+        <v>2</v>
+      </c>
+      <c r="J31">
+        <v>2</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Banuwa Mas</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Banuwa Mas</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D32">
+        <v>5</v>
+      </c>
+      <c r="E32">
+        <v>5</v>
+      </c>
+      <c r="F32" t="str">
+        <v>0.0%</v>
+      </c>
+      <c r="G32">
+        <v>10</v>
+      </c>
+      <c r="H32">
+        <v>3</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>1</v>
+      </c>
+      <c r="K32">
+        <v>1</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Bintang Jaya</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Bintang Jaya</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D33">
+        <v>4</v>
+      </c>
+      <c r="E33">
+        <v>6</v>
+      </c>
+      <c r="F33" t="str">
+        <v>50.0%</v>
+      </c>
+      <c r="G33">
+        <v>10</v>
+      </c>
+      <c r="H33">
+        <v>2</v>
+      </c>
+      <c r="I33">
+        <v>2</v>
+      </c>
+      <c r="J33">
+        <v>1</v>
+      </c>
+      <c r="K33">
+        <v>1</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>0</v>
+      </c>
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>HADI JAYA</v>
+      </c>
+      <c r="B34" t="str">
+        <v>HADI JAYA</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D34">
+        <v>4</v>
+      </c>
+      <c r="E34">
+        <v>6</v>
+      </c>
+      <c r="F34" t="str">
+        <v>50.0%</v>
+      </c>
+      <c r="G34">
+        <v>10</v>
+      </c>
+      <c r="H34">
+        <v>2</v>
+      </c>
+      <c r="I34">
+        <v>2</v>
+      </c>
+      <c r="J34">
+        <v>2</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Surya</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Surya</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D35">
+        <v>5</v>
+      </c>
+      <c r="E35">
+        <v>5</v>
+      </c>
+      <c r="F35" t="str">
+        <v>0.0%</v>
+      </c>
+      <c r="G35">
+        <v>10</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>3</v>
+      </c>
+      <c r="J35">
+        <v>1</v>
+      </c>
+      <c r="K35">
+        <v>1</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>WIWID</v>
+      </c>
+      <c r="B36" t="str">
+        <v>WIWID</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D36">
+        <v>2</v>
+      </c>
+      <c r="E36">
+        <v>8</v>
+      </c>
+      <c r="F36" t="str">
+        <v>300.0%</v>
+      </c>
+      <c r="G36">
+        <v>10</v>
+      </c>
+      <c r="H36">
+        <v>3</v>
+      </c>
+      <c r="I36">
+        <v>2</v>
+      </c>
+      <c r="J36">
+        <v>3</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>0</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>fajar bangunan 1</v>
+      </c>
+      <c r="B37" t="str">
+        <v>fajar bangunan 1</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D37">
+        <v>4</v>
+      </c>
+      <c r="E37">
+        <v>6</v>
+      </c>
+      <c r="F37" t="str">
+        <v>50.0%</v>
+      </c>
+      <c r="G37">
+        <v>10</v>
+      </c>
+      <c r="H37">
+        <v>3</v>
+      </c>
+      <c r="I37">
+        <v>1</v>
+      </c>
+      <c r="J37">
+        <v>1</v>
+      </c>
+      <c r="K37">
+        <v>1</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <v>0</v>
+      </c>
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>sari bumi putra</v>
+      </c>
+      <c r="B38" t="str">
+        <v>sari bumi putra</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D38">
+        <v>3</v>
+      </c>
+      <c r="E38">
+        <v>7</v>
+      </c>
+      <c r="F38" t="str">
+        <v>133.3%</v>
+      </c>
+      <c r="G38">
+        <v>10</v>
+      </c>
+      <c r="H38">
+        <v>3</v>
+      </c>
+      <c r="I38">
+        <v>2</v>
+      </c>
+      <c r="J38">
+        <v>1</v>
+      </c>
+      <c r="K38">
+        <v>1</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>0</v>
+      </c>
+      <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>AL INAYAH 2</v>
+      </c>
+      <c r="B39" t="str">
+        <v>AL INAYAH 2</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D39">
+        <v>2</v>
+      </c>
+      <c r="E39">
+        <v>7</v>
+      </c>
+      <c r="F39" t="str">
+        <v>250.0%</v>
+      </c>
+      <c r="G39">
+        <v>9</v>
+      </c>
+      <c r="H39">
+        <v>2</v>
+      </c>
+      <c r="I39">
+        <v>2</v>
+      </c>
+      <c r="J39">
+        <v>2</v>
+      </c>
+      <c r="K39">
+        <v>1</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>0</v>
+      </c>
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>ANIS JAYA</v>
+      </c>
+      <c r="B40" t="str">
+        <v>ANIS JAYA</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D40">
+        <v>3</v>
+      </c>
+      <c r="E40">
+        <v>6</v>
+      </c>
+      <c r="F40" t="str">
+        <v>100.0%</v>
+      </c>
+      <c r="G40">
+        <v>9</v>
+      </c>
+      <c r="H40">
+        <v>3</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>2</v>
+      </c>
+      <c r="K40">
+        <v>1</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>0</v>
+      </c>
+      <c r="R40">
+        <v>0</v>
+      </c>
+      <c r="S40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Al Inayah 1</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Al Inayah 1</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D41">
+        <v>2</v>
+      </c>
+      <c r="E41">
+        <v>7</v>
+      </c>
+      <c r="F41" t="str">
+        <v>250.0%</v>
+      </c>
+      <c r="G41">
+        <v>9</v>
+      </c>
+      <c r="H41">
+        <v>2</v>
+      </c>
+      <c r="I41">
+        <v>2</v>
+      </c>
+      <c r="J41">
+        <v>2</v>
+      </c>
+      <c r="K41">
+        <v>1</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>0</v>
+      </c>
+      <c r="R41">
+        <v>0</v>
+      </c>
+      <c r="S41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>DELTA AGUNG</v>
+      </c>
+      <c r="B42" t="str">
+        <v>DELTA AGUNG</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D42">
+        <v>2</v>
+      </c>
+      <c r="E42">
+        <v>7</v>
+      </c>
+      <c r="F42" t="str">
+        <v>250.0%</v>
+      </c>
+      <c r="G42">
+        <v>9</v>
+      </c>
+      <c r="H42">
+        <v>2</v>
+      </c>
+      <c r="I42">
+        <v>2</v>
+      </c>
+      <c r="J42">
+        <v>2</v>
+      </c>
+      <c r="K42">
+        <v>1</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>MEKAR JAYA</v>
+      </c>
+      <c r="B43" t="str">
+        <v>MEKAR JAYA</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D43">
+        <v>2</v>
+      </c>
+      <c r="E43">
+        <v>7</v>
+      </c>
+      <c r="F43" t="str">
+        <v>250.0%</v>
+      </c>
+      <c r="G43">
+        <v>9</v>
+      </c>
+      <c r="H43">
+        <v>2</v>
+      </c>
+      <c r="I43">
+        <v>2</v>
+      </c>
+      <c r="J43">
+        <v>2</v>
+      </c>
+      <c r="K43">
+        <v>1</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>0</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Makmur Jaya (Benowo)</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Makmur Jaya (Benowo)</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D44">
+        <v>3</v>
+      </c>
+      <c r="E44">
+        <v>6</v>
+      </c>
+      <c r="F44" t="str">
+        <v>100.0%</v>
+      </c>
+      <c r="G44">
+        <v>9</v>
+      </c>
+      <c r="H44">
+        <v>2</v>
+      </c>
+      <c r="I44">
+        <v>2</v>
+      </c>
+      <c r="J44">
+        <v>2</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>0</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Margi Seneng</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Margi Seneng</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D45">
+        <v>5</v>
+      </c>
+      <c r="E45">
+        <v>4</v>
+      </c>
+      <c r="F45" t="str">
+        <v>-20.0%</v>
+      </c>
+      <c r="G45">
+        <v>9</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>1</v>
+      </c>
+      <c r="J45">
+        <v>2</v>
+      </c>
+      <c r="K45">
+        <v>1</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <v>0</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>SABRINA JAYA</v>
+      </c>
+      <c r="B46" t="str">
+        <v>SABRINA JAYA</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D46">
+        <v>3</v>
+      </c>
+      <c r="E46">
+        <v>6</v>
+      </c>
+      <c r="F46" t="str">
+        <v>100.0%</v>
+      </c>
+      <c r="G46">
+        <v>9</v>
+      </c>
+      <c r="H46">
+        <v>3</v>
+      </c>
+      <c r="I46">
+        <v>1</v>
+      </c>
+      <c r="J46">
+        <v>2</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+      <c r="Q46">
+        <v>0</v>
+      </c>
+      <c r="R46">
+        <v>0</v>
+      </c>
+      <c r="S46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>SKM JAYA</v>
+      </c>
+      <c r="B47" t="str">
+        <v>SKM JAYA</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D47">
+        <v>4</v>
+      </c>
+      <c r="E47">
+        <v>5</v>
+      </c>
+      <c r="F47" t="str">
+        <v>25.0%</v>
+      </c>
+      <c r="G47">
+        <v>9</v>
+      </c>
+      <c r="H47">
+        <v>3</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>1</v>
+      </c>
+      <c r="K47">
+        <v>1</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>0</v>
+      </c>
+      <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Sejahtera (Tandes)</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Sejahtera (Tandes)</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D48">
+        <v>5</v>
+      </c>
+      <c r="E48">
+        <v>4</v>
+      </c>
+      <c r="F48" t="str">
+        <v>-20.0%</v>
+      </c>
+      <c r="G48">
+        <v>9</v>
+      </c>
+      <c r="H48">
+        <v>3</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>1</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>0</v>
+      </c>
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Sumber rejeki (mulyosari)</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Sumber rejeki (mulyosari)</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <v>9</v>
+      </c>
+      <c r="F49" t="str">
+        <v>100.0%</v>
+      </c>
+      <c r="G49">
+        <v>9</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>3</v>
+      </c>
+      <c r="J49">
+        <v>5</v>
+      </c>
+      <c r="K49">
+        <v>1</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>0</v>
+      </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>TASURA</v>
+      </c>
+      <c r="B50" t="str">
+        <v>TASURA</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D50">
+        <v>3</v>
+      </c>
+      <c r="E50">
+        <v>6</v>
+      </c>
+      <c r="F50" t="str">
+        <v>100.0%</v>
+      </c>
+      <c r="G50">
+        <v>9</v>
+      </c>
+      <c r="H50">
+        <v>2</v>
+      </c>
+      <c r="I50">
+        <v>2</v>
+      </c>
+      <c r="J50">
+        <v>1</v>
+      </c>
+      <c r="K50">
+        <v>1</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>0</v>
+      </c>
+      <c r="R50">
+        <v>0</v>
+      </c>
+      <c r="S50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>Tunas Langsung Jaya</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Tunas Langsung Jaya</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D51">
+        <v>4</v>
+      </c>
+      <c r="E51">
+        <v>5</v>
+      </c>
+      <c r="F51" t="str">
+        <v>25.0%</v>
+      </c>
+      <c r="G51">
+        <v>9</v>
+      </c>
+      <c r="H51">
+        <v>2</v>
+      </c>
+      <c r="I51">
+        <v>1</v>
+      </c>
+      <c r="J51">
+        <v>1</v>
+      </c>
+      <c r="K51">
+        <v>1</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>0</v>
+      </c>
+      <c r="R51">
+        <v>0</v>
+      </c>
+      <c r="S51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>AGUNG SANTOSO</v>
+      </c>
+      <c r="B52" t="str">
+        <v>AGUNG SANTOSO</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D52">
+        <v>2</v>
+      </c>
+      <c r="E52">
+        <v>6</v>
+      </c>
+      <c r="F52" t="str">
+        <v>200.0%</v>
+      </c>
+      <c r="G52">
+        <v>8</v>
+      </c>
+      <c r="H52">
+        <v>2</v>
+      </c>
+      <c r="I52">
+        <v>1</v>
+      </c>
+      <c r="J52">
+        <v>2</v>
+      </c>
+      <c r="K52">
+        <v>1</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+      <c r="Q52">
+        <v>0</v>
+      </c>
+      <c r="R52">
+        <v>0</v>
+      </c>
+      <c r="S52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>AMIN JAYA</v>
+      </c>
+      <c r="B53" t="str">
+        <v>AMIN JAYA</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D53">
+        <v>2</v>
+      </c>
+      <c r="E53">
+        <v>6</v>
+      </c>
+      <c r="F53" t="str">
+        <v>200.0%</v>
+      </c>
+      <c r="G53">
+        <v>8</v>
+      </c>
+      <c r="H53">
+        <v>2</v>
+      </c>
+      <c r="I53">
+        <v>2</v>
+      </c>
+      <c r="J53">
+        <v>2</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>0</v>
+      </c>
+      <c r="Q53">
+        <v>0</v>
+      </c>
+      <c r="R53">
+        <v>0</v>
+      </c>
+      <c r="S53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>Anjaya</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Anjaya</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D54">
+        <v>2</v>
+      </c>
+      <c r="E54">
+        <v>6</v>
+      </c>
+      <c r="F54" t="str">
+        <v>200.0%</v>
+      </c>
+      <c r="G54">
+        <v>8</v>
+      </c>
+      <c r="H54">
+        <v>4</v>
+      </c>
+      <c r="I54">
+        <v>1</v>
+      </c>
+      <c r="J54">
+        <v>1</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>0</v>
+      </c>
+      <c r="Q54">
+        <v>0</v>
+      </c>
+      <c r="R54">
+        <v>0</v>
+      </c>
+      <c r="S54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>GALAXY</v>
+      </c>
+      <c r="B55" t="str">
+        <v>GALAXY</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D55">
+        <v>3</v>
+      </c>
+      <c r="E55">
+        <v>5</v>
+      </c>
+      <c r="F55" t="str">
+        <v>66.7%</v>
+      </c>
+      <c r="G55">
+        <v>8</v>
+      </c>
+      <c r="H55">
+        <v>2</v>
+      </c>
+      <c r="I55">
+        <v>2</v>
+      </c>
+      <c r="J55">
+        <v>1</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>0</v>
+      </c>
+      <c r="Q55">
+        <v>0</v>
+      </c>
+      <c r="R55">
+        <v>0</v>
+      </c>
+      <c r="S55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>INTIVARIA</v>
+      </c>
+      <c r="B56" t="str">
+        <v>INTIVARIA</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D56">
+        <v>4</v>
+      </c>
+      <c r="E56">
+        <v>4</v>
+      </c>
+      <c r="F56" t="str">
+        <v>0.0%</v>
+      </c>
+      <c r="G56">
+        <v>8</v>
+      </c>
+      <c r="H56">
+        <v>3</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>1</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="Q56">
+        <v>0</v>
+      </c>
+      <c r="R56">
+        <v>0</v>
+      </c>
+      <c r="S56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>KARUNIA JAYA</v>
+      </c>
+      <c r="B57" t="str">
+        <v>KARUNIA JAYA</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D57">
+        <v>3</v>
+      </c>
+      <c r="E57">
+        <v>5</v>
+      </c>
+      <c r="F57" t="str">
+        <v>66.7%</v>
+      </c>
+      <c r="G57">
+        <v>8</v>
+      </c>
+      <c r="H57">
+        <v>2</v>
+      </c>
+      <c r="I57">
+        <v>1</v>
+      </c>
+      <c r="J57">
+        <v>2</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
+      </c>
+      <c r="Q57">
+        <v>0</v>
+      </c>
+      <c r="R57">
+        <v>0</v>
+      </c>
+      <c r="S57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>MARGA MULIA</v>
+      </c>
+      <c r="B58" t="str">
+        <v>MARGA MULIA</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D58">
+        <v>0</v>
+      </c>
+      <c r="E58">
+        <v>8</v>
+      </c>
+      <c r="F58" t="str">
+        <v>100.0%</v>
+      </c>
+      <c r="G58">
+        <v>8</v>
+      </c>
+      <c r="H58">
+        <v>3</v>
+      </c>
+      <c r="I58">
+        <v>2</v>
+      </c>
+      <c r="J58">
+        <v>3</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <v>0</v>
+      </c>
+      <c r="R58">
+        <v>0</v>
+      </c>
+      <c r="S58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>Makmur</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Makmur</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D59">
+        <v>5</v>
+      </c>
+      <c r="E59">
+        <v>3</v>
+      </c>
+      <c r="F59" t="str">
+        <v>-40.0%</v>
+      </c>
+      <c r="G59">
+        <v>8</v>
+      </c>
+      <c r="H59">
+        <v>3</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
+      </c>
+      <c r="Q59">
+        <v>0</v>
+      </c>
+      <c r="R59">
+        <v>0</v>
+      </c>
+      <c r="S59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>SUBUR 2</v>
+      </c>
+      <c r="B60" t="str">
+        <v>SUBUR 2</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D60">
+        <v>3</v>
+      </c>
+      <c r="E60">
+        <v>5</v>
+      </c>
+      <c r="F60" t="str">
+        <v>66.7%</v>
+      </c>
+      <c r="G60">
+        <v>8</v>
+      </c>
+      <c r="H60">
+        <v>2</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>2</v>
+      </c>
+      <c r="K60">
+        <v>1</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>0</v>
+      </c>
+      <c r="Q60">
+        <v>0</v>
+      </c>
+      <c r="R60">
+        <v>0</v>
+      </c>
+      <c r="S60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>Surya jaya (Lontar)</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Surya jaya (Lontar)</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D61">
+        <v>3</v>
+      </c>
+      <c r="E61">
+        <v>5</v>
+      </c>
+      <c r="F61" t="str">
+        <v>66.7%</v>
+      </c>
+      <c r="G61">
+        <v>8</v>
+      </c>
+      <c r="H61">
+        <v>2</v>
+      </c>
+      <c r="I61">
+        <v>1</v>
+      </c>
+      <c r="J61">
+        <v>1</v>
+      </c>
+      <c r="K61">
+        <v>1</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>0</v>
+      </c>
+      <c r="R61">
+        <v>0</v>
+      </c>
+      <c r="S61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>Adi Jaya (Jambangan)</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Adi Jaya (Jambangan)</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D62">
+        <v>2</v>
+      </c>
+      <c r="E62">
+        <v>5</v>
+      </c>
+      <c r="F62" t="str">
+        <v>150.0%</v>
+      </c>
+      <c r="G62">
+        <v>7</v>
+      </c>
+      <c r="H62">
+        <v>3</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>2</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>0</v>
+      </c>
+      <c r="R62">
+        <v>0</v>
+      </c>
+      <c r="S62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>Budi Jaya</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Budi Jaya</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D63">
+        <v>1</v>
+      </c>
+      <c r="E63">
+        <v>6</v>
+      </c>
+      <c r="F63" t="str">
+        <v>500.0%</v>
+      </c>
+      <c r="G63">
+        <v>7</v>
+      </c>
+      <c r="H63">
+        <v>3</v>
+      </c>
+      <c r="I63">
+        <v>2</v>
+      </c>
+      <c r="J63">
+        <v>1</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+      <c r="Q63">
+        <v>0</v>
+      </c>
+      <c r="R63">
+        <v>0</v>
+      </c>
+      <c r="S63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>DJADJAR PUTRA</v>
+      </c>
+      <c r="B64" t="str">
+        <v>DJADJAR PUTRA</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D64">
+        <v>4</v>
+      </c>
+      <c r="E64">
+        <v>3</v>
+      </c>
+      <c r="F64" t="str">
+        <v>-25.0%</v>
+      </c>
+      <c r="G64">
+        <v>7</v>
+      </c>
+      <c r="H64">
+        <v>2</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>1</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>0</v>
+      </c>
+      <c r="Q64">
+        <v>0</v>
+      </c>
+      <c r="R64">
+        <v>0</v>
+      </c>
+      <c r="S64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>Gondang Jaya</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Gondang Jaya</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D65">
+        <v>3</v>
+      </c>
+      <c r="E65">
+        <v>4</v>
+      </c>
+      <c r="F65" t="str">
+        <v>33.3%</v>
+      </c>
+      <c r="G65">
+        <v>7</v>
+      </c>
+      <c r="H65">
+        <v>1</v>
+      </c>
+      <c r="I65">
+        <v>2</v>
+      </c>
+      <c r="J65">
+        <v>1</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
+      </c>
+      <c r="Q65">
+        <v>0</v>
+      </c>
+      <c r="R65">
+        <v>0</v>
+      </c>
+      <c r="S65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>MAJU BERSAMA</v>
+      </c>
+      <c r="B66" t="str">
+        <v>MAJU BERSAMA</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+      <c r="E66">
+        <v>7</v>
+      </c>
+      <c r="F66" t="str">
+        <v>100.0%</v>
+      </c>
+      <c r="G66">
+        <v>7</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>3</v>
+      </c>
+      <c r="J66">
+        <v>3</v>
+      </c>
+      <c r="K66">
+        <v>1</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <v>0</v>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>0</v>
+      </c>
+      <c r="Q66">
+        <v>0</v>
+      </c>
+      <c r="R66">
+        <v>0</v>
+      </c>
+      <c r="S66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
         <v>Maju Jaya (Sukolilo)</v>
       </c>
-      <c r="B2" t="str">
+      <c r="B67" t="str">
         <v>Maju Jaya (Sukolilo)</v>
       </c>
-      <c r="C2" t="str">
-        <v>Others</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
+      <c r="C67" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D67">
+        <v>2</v>
+      </c>
+      <c r="E67">
         <v>5</v>
       </c>
-      <c r="F2" t="str">
+      <c r="F67" t="str">
         <v>150.0%</v>
       </c>
-      <c r="G2">
+      <c r="G67">
         <v>7</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
+      <c r="H67">
+        <v>1</v>
+      </c>
+      <c r="I67">
+        <v>2</v>
+      </c>
+      <c r="J67">
+        <v>2</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <v>0</v>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>0</v>
+      </c>
+      <c r="Q67">
+        <v>0</v>
+      </c>
+      <c r="R67">
+        <v>0</v>
+      </c>
+      <c r="S67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>Mitra Ploso</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Mitra Ploso</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68">
+        <v>7</v>
+      </c>
+      <c r="F68" t="str">
+        <v>100.0%</v>
+      </c>
+      <c r="G68">
+        <v>7</v>
+      </c>
+      <c r="H68">
+        <v>2</v>
+      </c>
+      <c r="I68">
+        <v>2</v>
+      </c>
+      <c r="J68">
+        <v>3</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>0</v>
+      </c>
+      <c r="Q68">
+        <v>0</v>
+      </c>
+      <c r="R68">
+        <v>0</v>
+      </c>
+      <c r="S68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>Santoso</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Santoso</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D69">
+        <v>2</v>
+      </c>
+      <c r="E69">
+        <v>5</v>
+      </c>
+      <c r="F69" t="str">
+        <v>150.0%</v>
+      </c>
+      <c r="G69">
+        <v>7</v>
+      </c>
+      <c r="H69">
+        <v>2</v>
+      </c>
+      <c r="I69">
+        <v>1</v>
+      </c>
+      <c r="J69">
+        <v>2</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+      <c r="Q69">
+        <v>0</v>
+      </c>
+      <c r="R69">
+        <v>0</v>
+      </c>
+      <c r="S69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>Urip Baru</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Urip Baru</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D70">
+        <v>0</v>
+      </c>
+      <c r="E70">
+        <v>7</v>
+      </c>
+      <c r="F70" t="str">
+        <v>100.0%</v>
+      </c>
+      <c r="G70">
+        <v>7</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>2</v>
+      </c>
+      <c r="J70">
+        <v>4</v>
+      </c>
+      <c r="K70">
+        <v>1</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>0</v>
+      </c>
+      <c r="Q70">
+        <v>0</v>
+      </c>
+      <c r="R70">
+        <v>0</v>
+      </c>
+      <c r="S70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>bumi arta</v>
+      </c>
+      <c r="B71" t="str">
+        <v>bumi arta</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D71">
+        <v>1</v>
+      </c>
+      <c r="E71">
+        <v>6</v>
+      </c>
+      <c r="F71" t="str">
+        <v>500.0%</v>
+      </c>
+      <c r="G71">
+        <v>7</v>
+      </c>
+      <c r="H71">
+        <v>3</v>
+      </c>
+      <c r="I71">
+        <v>2</v>
+      </c>
+      <c r="J71">
+        <v>1</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>0</v>
+      </c>
+      <c r="Q71">
+        <v>0</v>
+      </c>
+      <c r="R71">
+        <v>0</v>
+      </c>
+      <c r="S71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>ARTHA JAYA</v>
+      </c>
+      <c r="B72" t="str">
+        <v>ARTHA JAYA</v>
+      </c>
+      <c r="C72" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+      <c r="E72">
+        <v>6</v>
+      </c>
+      <c r="F72" t="str">
+        <v>100.0%</v>
+      </c>
+      <c r="G72">
+        <v>6</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <v>3</v>
+      </c>
+      <c r="J72">
+        <v>2</v>
+      </c>
+      <c r="K72">
+        <v>1</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>0</v>
+      </c>
+      <c r="Q72">
+        <v>0</v>
+      </c>
+      <c r="R72">
+        <v>0</v>
+      </c>
+      <c r="S72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>BAROKAH II</v>
+      </c>
+      <c r="B73" t="str">
+        <v>BAROKAH II</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D73">
+        <v>3</v>
+      </c>
+      <c r="E73">
+        <v>3</v>
+      </c>
+      <c r="F73" t="str">
+        <v>0.0%</v>
+      </c>
+      <c r="G73">
+        <v>6</v>
+      </c>
+      <c r="H73">
+        <v>1</v>
+      </c>
+      <c r="I73">
+        <v>1</v>
+      </c>
+      <c r="J73">
+        <v>1</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
+      </c>
+      <c r="P73">
+        <v>0</v>
+      </c>
+      <c r="Q73">
+        <v>0</v>
+      </c>
+      <c r="R73">
+        <v>0</v>
+      </c>
+      <c r="S73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>Bayu Santoso</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Bayu Santoso</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D74">
+        <v>2</v>
+      </c>
+      <c r="E74">
+        <v>4</v>
+      </c>
+      <c r="F74" t="str">
+        <v>100.0%</v>
+      </c>
+      <c r="G74">
+        <v>6</v>
+      </c>
+      <c r="H74">
+        <v>2</v>
+      </c>
+      <c r="I74">
+        <v>1</v>
+      </c>
+      <c r="J74">
+        <v>1</v>
+      </c>
+      <c r="K74">
+        <v>0</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74">
+        <v>0</v>
+      </c>
+      <c r="O74">
+        <v>0</v>
+      </c>
+      <c r="P74">
+        <v>0</v>
+      </c>
+      <c r="Q74">
+        <v>0</v>
+      </c>
+      <c r="R74">
+        <v>0</v>
+      </c>
+      <c r="S74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>EAA</v>
+      </c>
+      <c r="B75" t="str">
+        <v>EAA</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D75">
+        <v>2</v>
+      </c>
+      <c r="E75">
+        <v>4</v>
+      </c>
+      <c r="F75" t="str">
+        <v>100.0%</v>
+      </c>
+      <c r="G75">
+        <v>6</v>
+      </c>
+      <c r="H75">
+        <v>1</v>
+      </c>
+      <c r="I75">
+        <v>2</v>
+      </c>
+      <c r="J75">
+        <v>1</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>0</v>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+      <c r="P75">
+        <v>0</v>
+      </c>
+      <c r="Q75">
+        <v>0</v>
+      </c>
+      <c r="R75">
+        <v>0</v>
+      </c>
+      <c r="S75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>JAYA PRATAMA</v>
+      </c>
+      <c r="B76" t="str">
+        <v>JAYA PRATAMA</v>
+      </c>
+      <c r="C76" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D76">
+        <v>2</v>
+      </c>
+      <c r="E76">
+        <v>4</v>
+      </c>
+      <c r="F76" t="str">
+        <v>100.0%</v>
+      </c>
+      <c r="G76">
+        <v>6</v>
+      </c>
+      <c r="H76">
+        <v>1</v>
+      </c>
+      <c r="I76">
+        <v>1</v>
+      </c>
+      <c r="J76">
+        <v>2</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+      <c r="N76">
+        <v>0</v>
+      </c>
+      <c r="O76">
+        <v>0</v>
+      </c>
+      <c r="P76">
+        <v>0</v>
+      </c>
+      <c r="Q76">
+        <v>0</v>
+      </c>
+      <c r="R76">
+        <v>0</v>
+      </c>
+      <c r="S76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>Lancar Jaya</v>
+      </c>
+      <c r="B77" t="str">
+        <v>Lancar Jaya</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D77">
+        <v>1</v>
+      </c>
+      <c r="E77">
+        <v>5</v>
+      </c>
+      <c r="F77" t="str">
+        <v>400.0%</v>
+      </c>
+      <c r="G77">
+        <v>6</v>
+      </c>
+      <c r="H77">
+        <v>3</v>
+      </c>
+      <c r="I77">
+        <v>1</v>
+      </c>
+      <c r="J77">
+        <v>1</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77">
+        <v>0</v>
+      </c>
+      <c r="P77">
+        <v>0</v>
+      </c>
+      <c r="Q77">
+        <v>0</v>
+      </c>
+      <c r="R77">
+        <v>0</v>
+      </c>
+      <c r="S77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>SINAR GEMILANG</v>
+      </c>
+      <c r="B78" t="str">
+        <v>SINAR GEMILANG</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D78">
+        <v>3</v>
+      </c>
+      <c r="E78">
+        <v>3</v>
+      </c>
+      <c r="F78" t="str">
+        <v>0.0%</v>
+      </c>
+      <c r="G78">
+        <v>6</v>
+      </c>
+      <c r="H78">
+        <v>3</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78">
+        <v>0</v>
+      </c>
+      <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78">
+        <v>0</v>
+      </c>
+      <c r="P78">
+        <v>0</v>
+      </c>
+      <c r="Q78">
+        <v>0</v>
+      </c>
+      <c r="R78">
+        <v>0</v>
+      </c>
+      <c r="S78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>Sari Bumi Galangan</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Sari Bumi Galangan</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D79">
+        <v>2</v>
+      </c>
+      <c r="E79">
+        <v>4</v>
+      </c>
+      <c r="F79" t="str">
+        <v>100.0%</v>
+      </c>
+      <c r="G79">
+        <v>6</v>
+      </c>
+      <c r="H79">
+        <v>4</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <v>0</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+      <c r="M79">
+        <v>0</v>
+      </c>
+      <c r="N79">
+        <v>0</v>
+      </c>
+      <c r="O79">
+        <v>0</v>
+      </c>
+      <c r="P79">
+        <v>0</v>
+      </c>
+      <c r="Q79">
+        <v>0</v>
+      </c>
+      <c r="R79">
+        <v>0</v>
+      </c>
+      <c r="S79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>Simo</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Simo</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D80">
+        <v>2</v>
+      </c>
+      <c r="E80">
+        <v>4</v>
+      </c>
+      <c r="F80" t="str">
+        <v>100.0%</v>
+      </c>
+      <c r="G80">
+        <v>6</v>
+      </c>
+      <c r="H80">
+        <v>2</v>
+      </c>
+      <c r="I80">
+        <v>1</v>
+      </c>
+      <c r="J80">
+        <v>1</v>
+      </c>
+      <c r="K80">
+        <v>0</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80">
+        <v>0</v>
+      </c>
+      <c r="P80">
+        <v>0</v>
+      </c>
+      <c r="Q80">
+        <v>0</v>
+      </c>
+      <c r="R80">
+        <v>0</v>
+      </c>
+      <c r="S80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>cahaya tunggal</v>
+      </c>
+      <c r="B81" t="str">
+        <v>cahaya tunggal</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D81">
+        <v>0</v>
+      </c>
+      <c r="E81">
+        <v>6</v>
+      </c>
+      <c r="F81" t="str">
+        <v>100.0%</v>
+      </c>
+      <c r="G81">
+        <v>6</v>
+      </c>
+      <c r="H81">
+        <v>2</v>
+      </c>
+      <c r="I81">
+        <v>2</v>
+      </c>
+      <c r="J81">
+        <v>1</v>
+      </c>
+      <c r="K81">
+        <v>1</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="M81">
+        <v>0</v>
+      </c>
+      <c r="N81">
+        <v>0</v>
+      </c>
+      <c r="O81">
+        <v>0</v>
+      </c>
+      <c r="P81">
+        <v>0</v>
+      </c>
+      <c r="Q81">
+        <v>0</v>
+      </c>
+      <c r="R81">
+        <v>0</v>
+      </c>
+      <c r="S81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>harapan jaya</v>
+      </c>
+      <c r="B82" t="str">
+        <v>harapan jaya</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D82">
+        <v>2</v>
+      </c>
+      <c r="E82">
+        <v>4</v>
+      </c>
+      <c r="F82" t="str">
+        <v>100.0%</v>
+      </c>
+      <c r="G82">
+        <v>6</v>
+      </c>
+      <c r="H82">
+        <v>2</v>
+      </c>
+      <c r="I82">
+        <v>2</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <v>0</v>
+      </c>
+      <c r="L82">
+        <v>0</v>
+      </c>
+      <c r="M82">
+        <v>0</v>
+      </c>
+      <c r="N82">
+        <v>0</v>
+      </c>
+      <c r="O82">
+        <v>0</v>
+      </c>
+      <c r="P82">
+        <v>0</v>
+      </c>
+      <c r="Q82">
+        <v>0</v>
+      </c>
+      <c r="R82">
+        <v>0</v>
+      </c>
+      <c r="S82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>marga mulia</v>
+      </c>
+      <c r="B83" t="str">
+        <v>marga mulia</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D83">
+        <v>6</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+      <c r="F83" t="str">
+        <v>-100.0%</v>
+      </c>
+      <c r="G83">
+        <v>6</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83">
+        <v>0</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83">
+        <v>0</v>
+      </c>
+      <c r="N83">
+        <v>0</v>
+      </c>
+      <c r="O83">
+        <v>0</v>
+      </c>
+      <c r="P83">
+        <v>0</v>
+      </c>
+      <c r="Q83">
+        <v>0</v>
+      </c>
+      <c r="R83">
+        <v>0</v>
+      </c>
+      <c r="S83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>BAHAGIA</v>
+      </c>
+      <c r="B84" t="str">
+        <v>BAHAGIA</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D84">
+        <v>3</v>
+      </c>
+      <c r="E84">
+        <v>2</v>
+      </c>
+      <c r="F84" t="str">
+        <v>-33.3%</v>
+      </c>
+      <c r="G84">
+        <v>5</v>
+      </c>
+      <c r="H84">
+        <v>2</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <v>0</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
+      </c>
+      <c r="N84">
+        <v>0</v>
+      </c>
+      <c r="O84">
+        <v>0</v>
+      </c>
+      <c r="P84">
+        <v>0</v>
+      </c>
+      <c r="Q84">
+        <v>0</v>
+      </c>
+      <c r="R84">
+        <v>0</v>
+      </c>
+      <c r="S84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>Mukti jaya</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Mukti jaya</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D85">
+        <v>0</v>
+      </c>
+      <c r="E85">
+        <v>5</v>
+      </c>
+      <c r="F85" t="str">
+        <v>100.0%</v>
+      </c>
+      <c r="G85">
+        <v>5</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>4</v>
+      </c>
+      <c r="K85">
+        <v>1</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="M85">
+        <v>0</v>
+      </c>
+      <c r="N85">
+        <v>0</v>
+      </c>
+      <c r="O85">
+        <v>0</v>
+      </c>
+      <c r="P85">
+        <v>0</v>
+      </c>
+      <c r="Q85">
+        <v>0</v>
+      </c>
+      <c r="R85">
+        <v>0</v>
+      </c>
+      <c r="S85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>RAHMAT BEJI</v>
+      </c>
+      <c r="B86" t="str">
+        <v>RAHMAT BEJI</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+      <c r="E86">
+        <v>5</v>
+      </c>
+      <c r="F86" t="str">
+        <v>100.0%</v>
+      </c>
+      <c r="G86">
+        <v>5</v>
+      </c>
+      <c r="H86">
+        <v>1</v>
+      </c>
+      <c r="I86">
+        <v>2</v>
+      </c>
+      <c r="J86">
+        <v>2</v>
+      </c>
+      <c r="K86">
+        <v>0</v>
+      </c>
+      <c r="L86">
+        <v>0</v>
+      </c>
+      <c r="M86">
+        <v>0</v>
+      </c>
+      <c r="N86">
+        <v>0</v>
+      </c>
+      <c r="O86">
+        <v>0</v>
+      </c>
+      <c r="P86">
+        <v>0</v>
+      </c>
+      <c r="Q86">
+        <v>0</v>
+      </c>
+      <c r="R86">
+        <v>0</v>
+      </c>
+      <c r="S86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>Sama Bahagia</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Sama Bahagia</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D87">
+        <v>2</v>
+      </c>
+      <c r="E87">
+        <v>3</v>
+      </c>
+      <c r="F87" t="str">
+        <v>50.0%</v>
+      </c>
+      <c r="G87">
+        <v>5</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+      <c r="I87">
+        <v>1</v>
+      </c>
+      <c r="J87">
+        <v>1</v>
+      </c>
+      <c r="K87">
+        <v>1</v>
+      </c>
+      <c r="L87">
+        <v>0</v>
+      </c>
+      <c r="M87">
+        <v>0</v>
+      </c>
+      <c r="N87">
+        <v>0</v>
+      </c>
+      <c r="O87">
+        <v>0</v>
+      </c>
+      <c r="P87">
+        <v>0</v>
+      </c>
+      <c r="Q87">
+        <v>0</v>
+      </c>
+      <c r="R87">
+        <v>0</v>
+      </c>
+      <c r="S87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>Usaha Bersama</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Usaha Bersama</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D88">
+        <v>0</v>
+      </c>
+      <c r="E88">
+        <v>5</v>
+      </c>
+      <c r="F88" t="str">
+        <v>100.0%</v>
+      </c>
+      <c r="G88">
+        <v>5</v>
+      </c>
+      <c r="H88">
+        <v>1</v>
+      </c>
+      <c r="I88">
+        <v>1</v>
+      </c>
+      <c r="J88">
+        <v>2</v>
+      </c>
+      <c r="K88">
+        <v>1</v>
+      </c>
+      <c r="L88">
+        <v>0</v>
+      </c>
+      <c r="M88">
+        <v>0</v>
+      </c>
+      <c r="N88">
+        <v>0</v>
+      </c>
+      <c r="O88">
+        <v>0</v>
+      </c>
+      <c r="P88">
+        <v>0</v>
+      </c>
+      <c r="Q88">
+        <v>0</v>
+      </c>
+      <c r="R88">
+        <v>0</v>
+      </c>
+      <c r="S88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>Hosana</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Hosana</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+      <c r="E89">
+        <v>4</v>
+      </c>
+      <c r="F89" t="str">
+        <v>100.0%</v>
+      </c>
+      <c r="G89">
+        <v>4</v>
+      </c>
+      <c r="H89">
+        <v>2</v>
+      </c>
+      <c r="I89">
+        <v>1</v>
+      </c>
+      <c r="J89">
+        <v>1</v>
+      </c>
+      <c r="K89">
+        <v>0</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89">
+        <v>0</v>
+      </c>
+      <c r="N89">
+        <v>0</v>
+      </c>
+      <c r="O89">
+        <v>0</v>
+      </c>
+      <c r="P89">
+        <v>0</v>
+      </c>
+      <c r="Q89">
+        <v>0</v>
+      </c>
+      <c r="R89">
+        <v>0</v>
+      </c>
+      <c r="S89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>Sembilan Satoe</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Sembilan Satoe</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D90">
+        <v>0</v>
+      </c>
+      <c r="E90">
+        <v>4</v>
+      </c>
+      <c r="F90" t="str">
+        <v>100.0%</v>
+      </c>
+      <c r="G90">
+        <v>4</v>
+      </c>
+      <c r="H90">
+        <v>3</v>
+      </c>
+      <c r="I90">
+        <v>1</v>
+      </c>
+      <c r="J90">
+        <v>0</v>
+      </c>
+      <c r="K90">
+        <v>0</v>
+      </c>
+      <c r="L90">
+        <v>0</v>
+      </c>
+      <c r="M90">
+        <v>0</v>
+      </c>
+      <c r="N90">
+        <v>0</v>
+      </c>
+      <c r="O90">
+        <v>0</v>
+      </c>
+      <c r="P90">
+        <v>0</v>
+      </c>
+      <c r="Q90">
+        <v>0</v>
+      </c>
+      <c r="R90">
+        <v>0</v>
+      </c>
+      <c r="S90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>Warga Bumi Asri</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Warga Bumi Asri</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D91">
+        <v>0</v>
+      </c>
+      <c r="E91">
+        <v>4</v>
+      </c>
+      <c r="F91" t="str">
+        <v>100.0%</v>
+      </c>
+      <c r="G91">
+        <v>4</v>
+      </c>
+      <c r="H91">
+        <v>2</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>1</v>
+      </c>
+      <c r="K91">
+        <v>1</v>
+      </c>
+      <c r="L91">
+        <v>0</v>
+      </c>
+      <c r="M91">
+        <v>0</v>
+      </c>
+      <c r="N91">
+        <v>0</v>
+      </c>
+      <c r="O91">
+        <v>0</v>
+      </c>
+      <c r="P91">
+        <v>0</v>
+      </c>
+      <c r="Q91">
+        <v>0</v>
+      </c>
+      <c r="R91">
+        <v>0</v>
+      </c>
+      <c r="S91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>Wibrico</v>
+      </c>
+      <c r="B92" t="str">
+        <v>Wibrico</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D92">
+        <v>1</v>
+      </c>
+      <c r="E92">
+        <v>3</v>
+      </c>
+      <c r="F92" t="str">
+        <v>200.0%</v>
+      </c>
+      <c r="G92">
+        <v>4</v>
+      </c>
+      <c r="H92">
+        <v>3</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0</v>
+      </c>
+      <c r="K92">
+        <v>0</v>
+      </c>
+      <c r="L92">
+        <v>0</v>
+      </c>
+      <c r="M92">
+        <v>0</v>
+      </c>
+      <c r="N92">
+        <v>0</v>
+      </c>
+      <c r="O92">
+        <v>0</v>
+      </c>
+      <c r="P92">
+        <v>0</v>
+      </c>
+      <c r="Q92">
+        <v>0</v>
+      </c>
+      <c r="R92">
+        <v>0</v>
+      </c>
+      <c r="S92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>sinar sejahtera</v>
+      </c>
+      <c r="B93" t="str">
+        <v>sinar sejahtera</v>
+      </c>
+      <c r="C93" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D93">
+        <v>1</v>
+      </c>
+      <c r="E93">
+        <v>3</v>
+      </c>
+      <c r="F93" t="str">
+        <v>200.0%</v>
+      </c>
+      <c r="G93">
+        <v>4</v>
+      </c>
+      <c r="H93">
+        <v>1</v>
+      </c>
+      <c r="I93">
+        <v>2</v>
+      </c>
+      <c r="J93">
+        <v>0</v>
+      </c>
+      <c r="K93">
+        <v>0</v>
+      </c>
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93">
+        <v>0</v>
+      </c>
+      <c r="N93">
+        <v>0</v>
+      </c>
+      <c r="O93">
+        <v>0</v>
+      </c>
+      <c r="P93">
+        <v>0</v>
+      </c>
+      <c r="Q93">
+        <v>0</v>
+      </c>
+      <c r="R93">
+        <v>0</v>
+      </c>
+      <c r="S93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>Jaya Subur</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Jaya Subur</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D94">
+        <v>0</v>
+      </c>
+      <c r="E94">
+        <v>3</v>
+      </c>
+      <c r="F94" t="str">
+        <v>100.0%</v>
+      </c>
+      <c r="G94">
+        <v>3</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+      <c r="I94">
+        <v>1</v>
+      </c>
+      <c r="J94">
+        <v>1</v>
+      </c>
+      <c r="K94">
+        <v>1</v>
+      </c>
+      <c r="L94">
+        <v>0</v>
+      </c>
+      <c r="M94">
+        <v>0</v>
+      </c>
+      <c r="N94">
+        <v>0</v>
+      </c>
+      <c r="O94">
+        <v>0</v>
+      </c>
+      <c r="P94">
+        <v>0</v>
+      </c>
+      <c r="Q94">
+        <v>0</v>
+      </c>
+      <c r="R94">
+        <v>0</v>
+      </c>
+      <c r="S94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>Berkat Abadi (Rungkut)</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Berkat Abadi (Rungkut)</v>
+      </c>
+      <c r="C95" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D95">
+        <v>0</v>
+      </c>
+      <c r="E95">
+        <v>2</v>
+      </c>
+      <c r="F95" t="str">
+        <v>100.0%</v>
+      </c>
+      <c r="G95">
+        <v>2</v>
+      </c>
+      <c r="H95">
+        <v>0</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>1</v>
+      </c>
+      <c r="K95">
+        <v>1</v>
+      </c>
+      <c r="L95">
+        <v>0</v>
+      </c>
+      <c r="M95">
+        <v>0</v>
+      </c>
+      <c r="N95">
+        <v>0</v>
+      </c>
+      <c r="O95">
+        <v>0</v>
+      </c>
+      <c r="P95">
+        <v>0</v>
+      </c>
+      <c r="Q95">
+        <v>0</v>
+      </c>
+      <c r="R95">
+        <v>0</v>
+      </c>
+      <c r="S95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>Cahaya Makmur</v>
+      </c>
+      <c r="B96" t="str">
+        <v>Cahaya Makmur</v>
+      </c>
+      <c r="C96" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D96">
+        <v>0</v>
+      </c>
+      <c r="E96">
+        <v>2</v>
+      </c>
+      <c r="F96" t="str">
+        <v>100.0%</v>
+      </c>
+      <c r="G96">
+        <v>2</v>
+      </c>
+      <c r="H96">
+        <v>1</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>1</v>
+      </c>
+      <c r="K96">
+        <v>0</v>
+      </c>
+      <c r="L96">
+        <v>0</v>
+      </c>
+      <c r="M96">
+        <v>0</v>
+      </c>
+      <c r="N96">
+        <v>0</v>
+      </c>
+      <c r="O96">
+        <v>0</v>
+      </c>
+      <c r="P96">
+        <v>0</v>
+      </c>
+      <c r="Q96">
+        <v>0</v>
+      </c>
+      <c r="R96">
+        <v>0</v>
+      </c>
+      <c r="S96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>Putra Mandiri</v>
+      </c>
+      <c r="B97" t="str">
+        <v>Putra Mandiri</v>
+      </c>
+      <c r="C97" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D97">
+        <v>0</v>
+      </c>
+      <c r="E97">
+        <v>2</v>
+      </c>
+      <c r="F97" t="str">
+        <v>100.0%</v>
+      </c>
+      <c r="G97">
+        <v>2</v>
+      </c>
+      <c r="H97">
+        <v>0</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>1</v>
+      </c>
+      <c r="K97">
+        <v>1</v>
+      </c>
+      <c r="L97">
+        <v>0</v>
+      </c>
+      <c r="M97">
+        <v>0</v>
+      </c>
+      <c r="N97">
+        <v>0</v>
+      </c>
+      <c r="O97">
+        <v>0</v>
+      </c>
+      <c r="P97">
+        <v>0</v>
+      </c>
+      <c r="Q97">
+        <v>0</v>
+      </c>
+      <c r="R97">
+        <v>0</v>
+      </c>
+      <c r="S97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>Rini Sejahtera</v>
+      </c>
+      <c r="B98" t="str">
+        <v>Rini Sejahtera</v>
+      </c>
+      <c r="C98" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D98">
+        <v>0</v>
+      </c>
+      <c r="E98">
+        <v>2</v>
+      </c>
+      <c r="F98" t="str">
+        <v>100.0%</v>
+      </c>
+      <c r="G98">
+        <v>2</v>
+      </c>
+      <c r="H98">
+        <v>0</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>2</v>
+      </c>
+      <c r="K98">
+        <v>0</v>
+      </c>
+      <c r="L98">
+        <v>0</v>
+      </c>
+      <c r="M98">
+        <v>0</v>
+      </c>
+      <c r="N98">
+        <v>0</v>
+      </c>
+      <c r="O98">
+        <v>0</v>
+      </c>
+      <c r="P98">
+        <v>0</v>
+      </c>
+      <c r="Q98">
+        <v>0</v>
+      </c>
+      <c r="R98">
+        <v>0</v>
+      </c>
+      <c r="S98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>SUMBER MAKMUR SURABAYA</v>
+      </c>
+      <c r="B99" t="str">
+        <v>SUMBER MAKMUR SURABAYA</v>
+      </c>
+      <c r="C99" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D99">
+        <v>0</v>
+      </c>
+      <c r="E99">
+        <v>2</v>
+      </c>
+      <c r="F99" t="str">
+        <v>100.0%</v>
+      </c>
+      <c r="G99">
+        <v>2</v>
+      </c>
+      <c r="H99">
+        <v>0</v>
+      </c>
+      <c r="I99">
+        <v>1</v>
+      </c>
+      <c r="J99">
+        <v>1</v>
+      </c>
+      <c r="K99">
+        <v>0</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
+      <c r="M99">
+        <v>0</v>
+      </c>
+      <c r="N99">
+        <v>0</v>
+      </c>
+      <c r="O99">
+        <v>0</v>
+      </c>
+      <c r="P99">
+        <v>0</v>
+      </c>
+      <c r="Q99">
+        <v>0</v>
+      </c>
+      <c r="R99">
+        <v>0</v>
+      </c>
+      <c r="S99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>Subur (Wiyung)</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Subur (Wiyung)</v>
+      </c>
+      <c r="C100" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D100">
+        <v>0</v>
+      </c>
+      <c r="E100">
+        <v>2</v>
+      </c>
+      <c r="F100" t="str">
+        <v>100.0%</v>
+      </c>
+      <c r="G100">
+        <v>2</v>
+      </c>
+      <c r="H100">
+        <v>1</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>1</v>
+      </c>
+      <c r="K100">
+        <v>0</v>
+      </c>
+      <c r="L100">
+        <v>0</v>
+      </c>
+      <c r="M100">
+        <v>0</v>
+      </c>
+      <c r="N100">
+        <v>0</v>
+      </c>
+      <c r="O100">
+        <v>0</v>
+      </c>
+      <c r="P100">
+        <v>0</v>
+      </c>
+      <c r="Q100">
+        <v>0</v>
+      </c>
+      <c r="R100">
+        <v>0</v>
+      </c>
+      <c r="S100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>Kurnia Jaya (Wonocolo)</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Kurnia Jaya (Wonocolo)</v>
+      </c>
+      <c r="C101" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D101">
+        <v>0</v>
+      </c>
+      <c r="E101">
+        <v>1</v>
+      </c>
+      <c r="F101" t="str">
+        <v>100.0%</v>
+      </c>
+      <c r="G101">
+        <v>1</v>
+      </c>
+      <c r="H101">
+        <v>0</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <v>1</v>
+      </c>
+      <c r="L101">
+        <v>0</v>
+      </c>
+      <c r="M101">
+        <v>0</v>
+      </c>
+      <c r="N101">
+        <v>0</v>
+      </c>
+      <c r="O101">
+        <v>0</v>
+      </c>
+      <c r="P101">
+        <v>0</v>
+      </c>
+      <c r="Q101">
+        <v>0</v>
+      </c>
+      <c r="R101">
+        <v>0</v>
+      </c>
+      <c r="S101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>LESTARI (Pakal)</v>
+      </c>
+      <c r="B102" t="str">
+        <v>LESTARI (Pakal)</v>
+      </c>
+      <c r="C102" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D102">
+        <v>0</v>
+      </c>
+      <c r="E102">
+        <v>1</v>
+      </c>
+      <c r="F102" t="str">
+        <v>100.0%</v>
+      </c>
+      <c r="G102">
+        <v>1</v>
+      </c>
+      <c r="H102">
+        <v>0</v>
+      </c>
+      <c r="I102">
+        <v>0</v>
+      </c>
+      <c r="J102">
+        <v>1</v>
+      </c>
+      <c r="K102">
+        <v>0</v>
+      </c>
+      <c r="L102">
+        <v>0</v>
+      </c>
+      <c r="M102">
+        <v>0</v>
+      </c>
+      <c r="N102">
+        <v>0</v>
+      </c>
+      <c r="O102">
+        <v>0</v>
+      </c>
+      <c r="P102">
+        <v>0</v>
+      </c>
+      <c r="Q102">
+        <v>0</v>
+      </c>
+      <c r="R102">
+        <v>0</v>
+      </c>
+      <c r="S102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>kaje jaya</v>
+      </c>
+      <c r="B103" t="str">
+        <v>kaje jaya</v>
+      </c>
+      <c r="C103" t="str">
+        <v>Others</v>
+      </c>
+      <c r="D103">
+        <v>0</v>
+      </c>
+      <c r="E103">
+        <v>1</v>
+      </c>
+      <c r="F103" t="str">
+        <v>100.0%</v>
+      </c>
+      <c r="G103">
+        <v>1</v>
+      </c>
+      <c r="H103">
+        <v>1</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="J103">
+        <v>0</v>
+      </c>
+      <c r="K103">
+        <v>0</v>
+      </c>
+      <c r="L103">
+        <v>0</v>
+      </c>
+      <c r="M103">
+        <v>0</v>
+      </c>
+      <c r="N103">
+        <v>0</v>
+      </c>
+      <c r="O103">
+        <v>0</v>
+      </c>
+      <c r="P103">
+        <v>0</v>
+      </c>
+      <c r="Q103">
+        <v>0</v>
+      </c>
+      <c r="R103">
+        <v>0</v>
+      </c>
+      <c r="S103">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S103"/>
   </ignoredErrors>
 </worksheet>
 </file>